--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0211.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0211.xlsx
@@ -4086,7 +4086,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>[Lời Cuối Cùng] "Ta mua hết!"</t>
+          <t>[Lời Cuối Cùng] "Tao mua hết!"</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>"Cậu chỉ là con chó săn trung thành của giới quý tộc mà thôi..."</t>
+          <t>"Mày chỉ là con chó săn trung thành của giới quý tộc mà thôi..."</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>"Cậu bảo ta là cái móc câu thẳng tuột thế này mà vẫn câu được cá à?!"</t>
+          <t>"Cậu bảo tao là cái móc câu thẳng tuột thế này mà vẫn câu được cá à?!"</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>"Nếu đó là điều cậu muốn, hãy làm ngay đi, không chút do dự. Đó mới là cách làm đúng!"</t>
+          <t>"Nếu đó là điều mày muốn, hãy làm ngay đi, không chút do dự. Đó mới là cách làm đúng!"</t>
         </is>
       </c>
     </row>
@@ -10788,8 +10788,8 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>&lt;color=RedD&gt;The submerged slumberer stirs, ready to rise.
-O ghosts, offer your creations. Only one shall survive after the curtain falls.&lt;/color&gt;</t>
+          <t>&lt;color=RedD&gt;Kẻ say ngủ dưới đáy vực đã thức tỉnh, sẵn sàng trỗi dậy.
+Hỡi những hồn ma, hãy dâng lên tác phẩm của các ngươi. Chỉ một sẽ sống sót sau khi màn đêm buông xuống.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>"Ê... Ê chờ chút, chúng ta thực sự phải làm thế à? Ta... không thích cái không khí này tí nào. Hay là có ai khác viết nó đi... người thứ mười chẳng hạn?!"</t>
+          <t>"Ê... Ê chờ chút, chúng ta thực sự phải làm thế à? Tao... không thích cái không khí này tí nào. Hay là có ai khác viết nó đi... người thứ mười chẳng hạn?!"</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>"Tránh ra, để ta lo."</t>
+          <t>"Tránh ra, để tao lo."</t>
         </is>
       </c>
     </row>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Lần đầu đến đây ta cũng không thấy bọn họ.</t>
+          <t>Lần đầu đến đây tao cũng không thấy bọn họ.</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Bạn không thấy dấu vết của Nightmare ở Nhà hát 2, nhưng &lt;color=RedD&gt;cold air&lt;/color&gt; vẫn cứa vào da thịt.</t>
+          <t>Bạn không thấy dấu vết của Nightmare ở Nhà hát 2, nhưng &lt;color=RedD&gt;hơi lạnh&lt;/color&gt; vẫn cứa vào da thịt.</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Cứ chìm đắm trong lý luận, cậu sẽ bỏ lỡ sự thật đơn giản nhất—&lt;color=RedD&gt;the will to survive&lt;/color&gt;!</t>
+          <t>Cứ chìm đắm trong lý luận, cậu sẽ bỏ lỡ sự thật đơn giản nhất—&lt;color=RedD&gt;ý chí sinh tồn&lt;/color&gt;!</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>"Nhưng chúng ta khác nhau. Ta nghĩ... ngươi sẽ sớm hiểu thôi."</t>
+          <t>"Nhưng chúng ta khác nhau. Tao nghĩ... mày sẽ sớm hiểu thôi."</t>
         </is>
       </c>
     </row>
@@ -16249,7 +16249,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>"Cảnh tượng kinh khủng. Mỗi cú đánh đều trúng đầu. &lt;color=RedD&gt;His face is pulp&lt;/color&gt;. Chắc chỉ nhận dạng được qua quần áo và dáng người thôi."</t>
+          <t>"Cảnh tượng kinh khủng. Mỗi cú đánh đều trúng đầu. &lt;color=RedD&gt;Mặt hắn nát bét&lt;/color&gt;. Chắc chỉ nhận dạng được qua quần áo và dáng người thôi."</t>
         </is>
       </c>
     </row>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>"Đi thôi. Nếu có chuyện gì xảy ra nữa... như ta đã nói trước đó," cô quay lại, ánh mắt cô khiến ngươi không thể nhúc nhích.</t>
+          <t>"Đi thôi. Nếu có chuyện gì xảy ra nữa... như tao đã nói trước đó," cô quay lại, ánh mắt cô khiến mày không thể nhúc nhích.</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>"Được thôi... Được rồi. Ta không ngờ lại đến nước này."</t>
+          <t>"Được thôi... Được rồi. Tao không ngờ lại đến nước này."</t>
         </is>
       </c>
     </row>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>&lt;color=RedD&gt;Asphyxiation&lt;/color&gt;</t>
+          <t>&lt;color=RedD&gt;Ngạt thở.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>&lt;color=RedD&gt;That's where the truth about "her" lies.&lt;/color&gt;</t>
+          <t>&lt;color=RedD&gt;Chính nơi đó chứa đựng sự thật về "cô ta".&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>"Hiểu rồi. Được, ta sẽ cố hết sức để tìm ra sự thật đằng sau chuỗi án mạng này—"</t>
+          <t>"Hiểu rồi. Được, tao sẽ cố hết sức để tìm ra sự thật đằng sau chuỗi án mạng này—"</t>
         </is>
       </c>
     </row>
@@ -20149,7 +20149,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>&lt;color=RedD&gt;Bạn are about to make your final deduction. The direction of the story will diverge significantly depending on your conclusion.&lt;/color&gt;</t>
+          <t>&lt;color=RedD&gt;Bạn sắp đưa ra suy luận cuối cùng. Hướng đi của câu chuyện sẽ thay đổi đáng kể tùy theo kết luận của bạn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>&lt;color=RedD&gt;Think carefully, and then make your choice.&lt;/color&gt;</t>
+          <t>&lt;color=RedD&gt;Hãy suy nghĩ kỹ rồi hẵn đưa ra lựa chọn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Liệu trong số những người có mặt ở đây có Cộng Hưởng Giả nào chưa được biết đến không? Ai đó có khả năng hút hoặc nén không khí có thể giải thích cho tình trạng ngạt thở hoặc sốc tức thì…</t>
+          <t>Liệu trong số những người có mặt ở đây có Resonator nào chưa được biết đến không? Ai đó có khả năng hút hoặc nén không khí có thể giải thích cho tình trạng ngạt thở hoặc sốc tức thì…</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Vậy, trong hồi quan trọng thứ năm này, ai mới là trung tâm của mọi tội ác? Cái gì đã kéo lũ &lt;color=RedD&gt;Nightmares&lt;/color&gt; đến nơi này?</t>
+          <t>Vậy, trong hồi quan trọng thứ năm này, ai mới là trung tâm của mọi tội ác? Cái gì đã kéo lũ &lt;color=RedD&gt;Ác Mộng&lt;/color&gt; đến nơi này?</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21774,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Ta.</t>
+          <t>Tao.</t>
         </is>
       </c>
     </row>
@@ -23074,7 +23074,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>"Tự mình gói ghém lại đi, rồi reset và bắt đầu lại từ đầu. Làm cho đến khi cậu hiểu ra. Ta sẽ đợi cậu ở màn thứ năm."</t>
+          <t>"Tự mình gói ghém lại đi, rồi reset và bắt đầu lại từ đầu. Làm cho đến khi cậu hiểu ra. Tao sẽ đợi cậu ở màn thứ năm."</t>
         </is>
       </c>
     </row>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Ta không hiểu nổi. Quá nhiều câu đố quá.</t>
+          <t>Tao không hiểu nổi. Quá nhiều câu đố quá.</t>
         </is>
       </c>
     </row>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>"Sao lại là bí ẩn chứ? Ồ, ta thích những cốt truyện xoắn não lắm! {PlayerName}, cậu phải dành thời gian xem lại với ta nhé. Thỏa thuận?"</t>
+          <t>"Sao lại là bí ẩn chứ? Ồ, tao thích những cốt truyện xoắn não lắm! {PlayerName}, cậu phải dành thời gian xem lại với tao nhé. Thỏa thuận?"</t>
         </is>
       </c>
     </row>
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>"Hừ... Không thể thay đổi bản chất của mình được, phải không? Giả sử ta làm thật, thì sao? Cậu nghĩ cậu có quyền phán xét ta à? Đừng có tự huyễn hoặc mình. Sống sót mới là chân lý duy nhất."</t>
+          <t>"Hừ... Không thể thay đổi bản chất của mình được, phải không? Giả sử tao làm thật, thì sao? Cậu nghĩ cậu có quyền phán xét tao à? Đừng có tự huyễn hoặc mình. Sống sót mới là chân lý duy nhất."</t>
         </is>
       </c>
     </row>
@@ -26259,7 +26259,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>"Ui... Không khí này chẳng lành chút nào. {PlayerName}, cậu ổn chứ...? Ta ngủ bao lâu rồi nhỉ...?"</t>
+          <t>"Ui... Không khí này chẳng lành chút nào. {PlayerName}, cậu ổn chứ...? Tao ngủ bao lâu rồi nhỉ...?"</t>
         </is>
       </c>
     </row>
@@ -26389,7 +26389,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>"Này, {PlayerName}, cái đó là gì thế? Cảm giác quen quen... Ui, ta đã thấy cái này ở đâu rồi nhỉ?"</t>
+          <t>"Này, {PlayerName}, cái đó là gì thế? Cảm giác quen quen... Ui, tao đã thấy cái này ở đâu rồi nhỉ?"</t>
         </is>
       </c>
     </row>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>"Dù sao, ta cũng thấy hơi áy náy vì không cho khán giả một cái kết xứng đáng."</t>
+          <t>"Dù sao, tao cũng thấy hơi áy náy vì không cho khán giả một cái kết xứng đáng."</t>
         </is>
       </c>
     </row>
@@ -30224,7 +30224,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>"Ừ, không chơi trò nữa đâu! Cậu đang nhăm nhe gì hả?!"</t>
+          <t>"Ừ, không chơi trò nữa đâu! Mày đang nhăm nhe gì hả?!"</t>
         </is>
       </c>
     </row>
@@ -30419,7 +30419,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>"Được rồi, ta sẽ cố hết sức để tìm ra sự thật đằng sau bộ phim này và chuỗi sự việc này."</t>
+          <t>"Được rồi, tao sẽ cố hết sức để tìm ra sự thật đằng sau bộ phim này và chuỗi sự việc này."</t>
         </is>
       </c>
     </row>
